--- a/data/trans_dic/P19C06-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P19C06-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue por tratamiento de las enfermedades de las encías</t>
+          <t>Población cuyo motivo por su última visita al dentista fue por tratamiento de las enfermedades de las encías (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,51; 3,43</t>
+          <t>0,49; 3,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,33; 3,82</t>
+          <t>0,44; 4,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,71; 3,55</t>
+          <t>0,6; 3,56</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,73</t>
+          <t>0,2; 1,87</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,7; 4,15</t>
+          <t>0,71; 4,59</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,71; 4,24</t>
+          <t>0,7; 4,04</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,66; 4,22</t>
+          <t>0,69; 4,02</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,1; 3,52</t>
+          <t>1,25; 3,61</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,88; 2,98</t>
+          <t>0,79; 2,98</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,89; 3,31</t>
+          <t>0,85; 3,19</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,86; 2,95</t>
+          <t>0,9; 2,9</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,71; 2,16</t>
+          <t>0,78; 2,25</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,99</t>
+          <t>0,32; 3,06</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,06</t>
+          <t>0,23; 2,25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,92</t>
+          <t>0,0; 1,96</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,21; 2,06</t>
+          <t>0,23; 2,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,67</t>
+          <t>0,3; 2,89</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,0; 5,16</t>
+          <t>0,96; 5,0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,3; 3,09</t>
+          <t>0,3; 2,81</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,48</t>
+          <t>0,15; 1,43</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,47; 2,28</t>
+          <t>0,58; 2,36</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,73; 2,81</t>
+          <t>0,68; 2,65</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,44; 1,94</t>
+          <t>0,32; 1,9</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,31</t>
+          <t>0,31; 1,3</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,82; 3,41</t>
+          <t>0,85; 3,26</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,97; 3,39</t>
+          <t>0,97; 3,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,71; 3,56</t>
+          <t>0,71; 3,52</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,11; 1,9</t>
+          <t>0,13; 1,95</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,94</t>
+          <t>0,0; 5,05</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,88; 6,01</t>
+          <t>0,88; 5,54</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,48</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,27</t>
+          <t>0,0; 1,33</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,82; 2,87</t>
+          <t>0,82; 3,07</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,21; 3,56</t>
+          <t>1,14; 3,32</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,38; 2,76</t>
+          <t>0,52; 2,79</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,52</t>
+          <t>0,17; 1,52</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,59; 2,09</t>
+          <t>0,58; 2,06</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,17</t>
+          <t>0,18; 1,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,79</t>
+          <t>0,23; 1,74</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,72</t>
+          <t>0,37; 2,85</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,37; 2,14</t>
+          <t>0,37; 2,07</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,43; 1,96</t>
+          <t>0,42; 2,05</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,84; 2,79</t>
+          <t>0,84; 2,78</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,43; 1,75</t>
+          <t>0,38; 1,71</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,67; 1,79</t>
+          <t>0,7; 1,82</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,41; 1,28</t>
+          <t>0,38; 1,24</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,67; 1,79</t>
+          <t>0,67; 1,8</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,52; 1,88</t>
+          <t>0,53; 1,76</t>
         </is>
       </c>
     </row>
@@ -1277,57 +1277,57 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,79</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,35</t>
+          <t>0,25; 2,39</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,74; 3,66</t>
+          <t>0,71; 3,53</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,98</t>
+          <t>0,14; 1,99</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,5</t>
+          <t>0,46; 2,78</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,61; 2,4</t>
+          <t>0,54; 2,25</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,53; 2,47</t>
+          <t>0,52; 2,45</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,93; 2,38</t>
+          <t>0,89; 2,23</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,62</t>
+          <t>0,38; 1,79</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,66; 1,99</t>
+          <t>0,6; 2,05</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,77; 2,35</t>
+          <t>0,8; 2,39</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,87</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,8</t>
+          <t>0,0; 2,56</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1437,42 +1437,42 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,69</t>
+          <t>0,4; 1,67</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,56; 2,03</t>
+          <t>0,55; 1,97</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,69; 2,41</t>
+          <t>0,67; 2,37</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,26</t>
+          <t>0,18; 1,38</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,4</t>
+          <t>0,32; 1,42</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,51; 1,69</t>
+          <t>0,54; 1,74</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,69; 2,08</t>
+          <t>0,63; 2,08</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,23; 1,35</t>
+          <t>0,25; 1,31</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,72; 1,54</t>
+          <t>0,74; 1,62</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,67; 1,44</t>
+          <t>0,66; 1,47</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,78; 1,74</t>
+          <t>0,82; 1,72</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,5; 1,38</t>
+          <t>0,5; 1,31</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,74; 1,6</t>
+          <t>0,76; 1,6</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,06; 1,93</t>
+          <t>1,05; 1,96</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,93; 1,85</t>
+          <t>0,95; 1,82</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,8; 1,41</t>
+          <t>0,77; 1,41</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,86; 1,44</t>
+          <t>0,85; 1,44</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,97; 1,54</t>
+          <t>0,96; 1,56</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,98; 1,62</t>
+          <t>0,99; 1,61</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,72; 1,22</t>
+          <t>0,7; 1,23</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue por tratamiento de las enfermedades de las encías</t>
+          <t>Población cuyo motivo por su última visita al dentista fue por tratamiento de las enfermedades de las encías (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1987; 13244</t>
+          <t>1886; 11652</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1295; 15099</t>
+          <t>1754; 16541</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2761; 13779</t>
+          <t>2325; 13803</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1004; 8638</t>
+          <t>996; 9322</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1879; 11140</t>
+          <t>1897; 12327</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2100; 12463</t>
+          <t>2066; 11879</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2092; 13314</t>
+          <t>2166; 12685</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4831; 15526</t>
+          <t>5491; 15911</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5735; 19484</t>
+          <t>5150; 19525</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6100; 22843</t>
+          <t>5879; 21958</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6029; 20753</t>
+          <t>6310; 20434</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6673; 20250</t>
+          <t>7358; 21169</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>953; 8971</t>
+          <t>956; 9188</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>901; 7906</t>
+          <t>888; 8631</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 6092</t>
+          <t>0; 6216</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>950; 9236</t>
+          <t>1045; 8979</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>975; 8897</t>
+          <t>987; 9656</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3144; 16163</t>
+          <t>3008; 15665</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>999; 10298</t>
+          <t>989; 9359</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>606; 5584</t>
+          <t>565; 5407</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2966; 14444</t>
+          <t>3692; 14937</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5122; 19592</t>
+          <t>4739; 18489</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2847; 12583</t>
+          <t>2051; 12377</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2476; 10795</t>
+          <t>2593; 10740</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3519; 14661</t>
+          <t>3639; 14024</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5176; 18151</t>
+          <t>5189; 18455</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2866; 14416</t>
+          <t>2864; 14276</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>743; 12574</t>
+          <t>852; 12908</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 6916</t>
+          <t>0; 7074</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2111; 14470</t>
+          <t>2124; 13325</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 2057</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 2096</t>
+          <t>0; 2187</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4694; 16372</t>
+          <t>4673; 17520</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>9354; 27657</t>
+          <t>8860; 25748</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2077; 15016</t>
+          <t>2848; 15201</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1528; 12543</t>
+          <t>1414; 12556</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5133; 18223</t>
+          <t>5023; 17911</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1705; 11353</t>
+          <t>1716; 11492</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2637; 15760</t>
+          <t>2025; 15318</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3228; 27188</t>
+          <t>3739; 28460</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2183; 12772</t>
+          <t>2186; 12362</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3004; 13698</t>
+          <t>2960; 14331</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5712; 19073</t>
+          <t>5714; 19009</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4159; 16811</t>
+          <t>3682; 16349</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9784; 26206</t>
+          <t>10232; 26722</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6867; 21342</t>
+          <t>6331; 20733</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10479; 28042</t>
+          <t>10541; 28169</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>10169; 36713</t>
+          <t>10347; 34390</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 1966</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1055; 9486</t>
+          <t>1021; 9658</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3148; 15568</t>
+          <t>3028; 15011</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>615; 8678</t>
+          <t>607; 8741</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2007; 11415</t>
+          <t>2087; 12688</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4052; 16037</t>
+          <t>3599; 15048</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2954; 13796</t>
+          <t>2922; 13681</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>7562; 19370</t>
+          <t>7207; 18166</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1958; 11388</t>
+          <t>2668; 12615</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>7066; 21377</t>
+          <t>6396; 21982</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7530; 23112</t>
+          <t>7893; 23492</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>9494; 23818</t>
+          <t>9548; 23852</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 1851</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 5275</t>
+          <t>0; 5262</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 6760</t>
+          <t>0; 6194</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 8687</t>
+          <t>0; 8679</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3765; 16024</t>
+          <t>3746; 15829</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5181; 18769</t>
+          <t>5133; 18186</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5724; 19893</t>
+          <t>5506; 19567</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1094; 9355</t>
+          <t>1326; 10249</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3599; 16225</t>
+          <t>3704; 16477</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>5861; 19428</t>
+          <t>6227; 19966</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7379; 22169</t>
+          <t>6735; 22192</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2233; 13238</t>
+          <t>2453; 12792</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>17623; 37765</t>
+          <t>18082; 39672</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>19395; 41953</t>
+          <t>19285; 42686</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>20623; 46230</t>
+          <t>21694; 45654</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>16506; 45221</t>
+          <t>16467; 42879</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>20222; 43763</t>
+          <t>20878; 43864</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>33400; 60552</t>
+          <t>33129; 61561</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>26687; 52937</t>
+          <t>27064; 51871</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>27865; 49252</t>
+          <t>26968; 49316</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>44567; 74569</t>
+          <t>44232; 74859</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>58566; 93404</t>
+          <t>58070; 94257</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>53963; 89532</t>
+          <t>54627; 88888</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>48873; 82984</t>
+          <t>47357; 83700</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P19C06-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P19C06-Clase-trans_dic.xlsx
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,49; 3,02</t>
+          <t>0,52; 3,51</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,44; 4,18</t>
+          <t>0,49; 4,07</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,6; 3,56</t>
+          <t>0,6; 3,57</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,87</t>
+          <t>0,2; 1,72</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,71; 4,59</t>
+          <t>0,72; 4,39</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,7; 4,04</t>
+          <t>0,72; 4,09</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,69; 4,02</t>
+          <t>0,65; 3,91</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,25; 3,61</t>
+          <t>1,08; 3,37</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,79; 2,98</t>
+          <t>0,8; 2,86</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,85; 3,19</t>
+          <t>0,87; 3,33</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,9; 2,9</t>
+          <t>0,92; 2,96</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,78; 2,25</t>
+          <t>0,73; 2,0</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,65%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,06</t>
+          <t>0,32; 3,42</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,25</t>
+          <t>0,23; 2,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,96</t>
+          <t>0,0; 2,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,0</t>
+          <t>0,2; 1,82</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,3; 2,89</t>
+          <t>0,29; 2,86</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,96; 5,0</t>
+          <t>0,85; 4,89</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,3; 2,81</t>
+          <t>0,33; 2,98</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,43</t>
+          <t>0,17; 1,4</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,36</t>
+          <t>0,58; 2,31</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,65</t>
+          <t>0,72; 2,66</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,32; 1,9</t>
+          <t>0,32; 2,0</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,3</t>
+          <t>0,31; 1,31</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,97%</t>
         </is>
       </c>
     </row>
@@ -997,32 +997,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,85; 3,26</t>
+          <t>0,82; 3,28</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,97; 3,45</t>
+          <t>0,92; 3,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,71; 3,52</t>
+          <t>0,57; 3,63</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,95</t>
+          <t>0,39; 2,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,05</t>
+          <t>0,0; 5,16</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,88; 5,54</t>
+          <t>0,88; 5,29</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1032,27 +1032,27 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,33</t>
+          <t>0,0; 2,86</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,82; 3,07</t>
+          <t>0,8; 2,87</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,14; 3,32</t>
+          <t>1,28; 3,54</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,52; 2,79</t>
+          <t>0,53; 2,61</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,52</t>
+          <t>0,48; 2,0</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,9%</t>
         </is>
       </c>
     </row>
@@ -1137,32 +1137,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,06</t>
+          <t>0,56; 2,05</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,18</t>
+          <t>0,19; 1,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,23; 1,74</t>
+          <t>0,23; 1,62</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,37; 2,85</t>
+          <t>0,27; 1,68</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,37; 2,07</t>
+          <t>0,35; 2,05</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,42; 2,05</t>
+          <t>0,43; 2,05</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1172,27 +1172,27 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,38; 1,71</t>
+          <t>0,61; 2,03</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,7; 1,82</t>
+          <t>0,65; 1,82</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,38; 1,24</t>
+          <t>0,4; 1,3</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,67; 1,8</t>
+          <t>0,69; 1,87</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,53; 1,76</t>
+          <t>0,54; 1,47</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -1282,64 +1282,64 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,39</t>
+          <t>0,26; 2,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,71; 3,53</t>
+          <t>0,71; 3,52</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,99</t>
+          <t>0,12; 1,86</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,46; 2,78</t>
+          <t>0,42; 2,62</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,54; 2,25</t>
+          <t>0,49; 2,47</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,52; 2,45</t>
+          <t>0,4; 2,35</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,89; 2,23</t>
+          <t>0,99; 2,5</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,38; 1,79</t>
+          <t>0,37; 1,72</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,6; 2,05</t>
+          <t>0,66; 2,07</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,8; 2,39</t>
+          <t>0,76; 2,52</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,76; 1,9</t>
+          <t>0,78; 1,97</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,45%</t>
         </is>
       </c>
     </row>
@@ -1422,57 +1422,57 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,38</t>
+          <t>0,0; 2,35</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,56</t>
+          <t>0,0; 2,96</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,72</t>
+          <t>0,0; 3,35</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,67</t>
+          <t>0,41; 1,74</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,55; 1,97</t>
+          <t>0,56; 2,06</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,67; 2,37</t>
+          <t>0,66; 2,41</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,38</t>
+          <t>0,1; 0,73</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,32; 1,42</t>
+          <t>0,33; 1,34</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,54; 1,74</t>
+          <t>0,54; 1,76</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,63; 2,08</t>
+          <t>0,69; 2,15</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,25; 1,31</t>
+          <t>0,19; 1,02</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,74; 1,62</t>
+          <t>0,71; 1,54</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,66; 1,47</t>
+          <t>0,64; 1,48</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,82; 1,72</t>
+          <t>0,78; 1,78</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,5; 1,31</t>
+          <t>0,49; 1,13</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,76; 1,6</t>
+          <t>0,81; 1,67</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,05; 1,96</t>
+          <t>1,03; 1,9</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,95; 1,82</t>
+          <t>0,93; 1,87</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,77; 1,41</t>
+          <t>0,8; 1,42</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,85; 1,44</t>
+          <t>0,86; 1,42</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,96; 1,56</t>
+          <t>0,96; 1,54</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,99; 1,61</t>
+          <t>0,99; 1,62</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,7; 1,23</t>
+          <t>0,74; 1,18</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3157</t>
+          <t>3418</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9253</t>
+          <t>9522</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>12409</t>
+          <t>12939</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1886; 11652</t>
+          <t>2019; 13557</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1754; 16541</t>
+          <t>1920; 16104</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2325; 13803</t>
+          <t>2311; 13849</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>996; 9322</t>
+          <t>1106; 9291</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1897; 12327</t>
+          <t>1927; 11768</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2066; 11879</t>
+          <t>2109; 12017</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2166; 12685</t>
+          <t>2063; 12347</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5491; 15911</t>
+          <t>5176; 16223</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5150; 19525</t>
+          <t>5235; 18724</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5879; 21958</t>
+          <t>6016; 22964</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6310; 20434</t>
+          <t>6499; 20846</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>7358; 21169</t>
+          <t>7437; 20434</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3288</t>
+          <t>3351</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2304</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>5592</t>
+          <t>5802</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>956; 9188</t>
+          <t>961; 10261</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>888; 8631</t>
+          <t>891; 8330</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 6216</t>
+          <t>0; 6326</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1045; 8979</t>
+          <t>935; 8715</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>987; 9656</t>
+          <t>979; 9531</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3008; 15665</t>
+          <t>2665; 15340</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>989; 9359</t>
+          <t>1103; 9951</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>565; 5407</t>
+          <t>712; 5871</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3692; 14937</t>
+          <t>3648; 14617</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4739; 18489</t>
+          <t>5039; 18532</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2051; 12377</t>
+          <t>2096; 13016</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2593; 10740</t>
+          <t>2797; 11796</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5179</t>
+          <t>5013</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>533</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5712</t>
+          <t>6283</t>
         </is>
       </c>
     </row>
@@ -2343,32 +2343,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3639; 14024</t>
+          <t>3509; 14113</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5189; 18455</t>
+          <t>4951; 18433</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2864; 14276</t>
+          <t>2292; 14710</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>852; 12908</t>
+          <t>1804; 10644</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 7074</t>
+          <t>0; 7231</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2124; 13325</t>
+          <t>2114; 12731</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -2378,27 +2378,27 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 2187</t>
+          <t>0; 5289</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4673; 17520</t>
+          <t>4542; 16373</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8860; 25748</t>
+          <t>9924; 27468</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2848; 15201</t>
+          <t>2865; 14217</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1414; 12556</t>
+          <t>3125; 12977</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9718</t>
+          <t>7830</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>8928</t>
+          <t>9531</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>18645</t>
+          <t>17361</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5023; 17911</t>
+          <t>4839; 17908</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1716; 11492</t>
+          <t>1827; 11842</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2025; 15318</t>
+          <t>2041; 14269</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3739; 28460</t>
+          <t>2951; 18428</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2186; 12362</t>
+          <t>2061; 12197</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2960; 14331</t>
+          <t>3004; 14309</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5714; 19009</t>
+          <t>5735; 19042</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3682; 16349</t>
+          <t>5111; 16969</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>10232; 26722</t>
+          <t>9540; 26711</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6331; 20733</t>
+          <t>6689; 21721</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10541; 28169</t>
+          <t>10767; 29169</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>10347; 34390</t>
+          <t>10390; 28345</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3154</t>
+          <t>3269</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>12299</t>
+          <t>13395</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>15453</t>
+          <t>16665</t>
         </is>
       </c>
     </row>
@@ -2764,64 +2764,64 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1021; 9658</t>
+          <t>1052; 10274</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3028; 15011</t>
+          <t>3007; 14981</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>607; 8741</t>
+          <t>599; 9500</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2087; 12688</t>
+          <t>1938; 11956</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3599; 15048</t>
+          <t>3249; 16529</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2922; 13681</t>
+          <t>2215; 13125</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>7207; 18166</t>
+          <t>7841; 19854</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2668; 12615</t>
+          <t>2638; 12098</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>6396; 21982</t>
+          <t>7128; 22191</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7893; 23492</t>
+          <t>7495; 24730</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>9548; 23852</t>
+          <t>10216; 25741</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2274</t>
+          <t>2129</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>3594</t>
+          <t>2563</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>5868</t>
+          <t>4692</t>
         </is>
       </c>
     </row>
@@ -2972,57 +2972,57 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 5262</t>
+          <t>0; 5208</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 6194</t>
+          <t>0; 7155</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 8679</t>
+          <t>0; 7565</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3746; 15829</t>
+          <t>3874; 16407</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5133; 18186</t>
+          <t>5142; 19075</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5506; 19567</t>
+          <t>5472; 19864</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1326; 10249</t>
+          <t>801; 5977</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3704; 16477</t>
+          <t>3813; 15536</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>6227; 19966</t>
+          <t>6143; 20131</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>6735; 22192</t>
+          <t>7395; 22951</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2453; 12792</t>
+          <t>1947; 10698</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>26770</t>
+          <t>25011</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>36910</t>
+          <t>38732</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>63680</t>
+          <t>63742</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>18082; 39672</t>
+          <t>17273; 37695</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>19285; 42686</t>
+          <t>18678; 43179</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>21694; 45654</t>
+          <t>20709; 47179</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>16467; 42879</t>
+          <t>16227; 37450</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>20878; 43864</t>
+          <t>22068; 45788</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>33129; 61561</t>
+          <t>32295; 59565</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>27064; 51871</t>
+          <t>26619; 53526</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>26968; 49316</t>
+          <t>28273; 50006</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>44232; 74859</t>
+          <t>44514; 73675</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>58070; 94257</t>
+          <t>58064; 93161</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>54627; 88888</t>
+          <t>54339; 89211</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>47357; 83700</t>
+          <t>50494; 81008</t>
         </is>
       </c>
     </row>
